--- a/data/data_raw/eurostat/AT_oil_en_bal_nrg_bal_c.xlsx
+++ b/data/data_raw/eurostat/AT_oil_en_bal_nrg_bal_c.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN140"/>
+  <dimension ref="A1:AO140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +624,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -755,6 +760,9 @@
       </c>
       <c r="AN2" t="n">
         <v>5501.283</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5460.424</v>
       </c>
     </row>
     <row r="3">
@@ -888,6 +896,9 @@
       <c r="AN3" t="n">
         <v>0</v>
       </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1009,16 +1020,19 @@
         <v>176346.973</v>
       </c>
       <c r="AK4" t="n">
-        <v>159238.068</v>
+        <v>158451.468</v>
       </c>
       <c r="AL4" t="n">
-        <v>157504.616</v>
+        <v>157669.7</v>
       </c>
       <c r="AM4" t="n">
-        <v>144844.207</v>
+        <v>145096.838</v>
       </c>
       <c r="AN4" t="n">
-        <v>154379.694</v>
+        <v>154615.546</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>152104.805</v>
       </c>
     </row>
     <row r="5">
@@ -1141,16 +1155,19 @@
         <v>32938.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>32203.221</v>
+        <v>32267.158</v>
       </c>
       <c r="AL5" t="n">
-        <v>33575.106</v>
+        <v>33638.151</v>
       </c>
       <c r="AM5" t="n">
-        <v>19464.39</v>
+        <v>19470.312</v>
       </c>
       <c r="AN5" t="n">
-        <v>27039.088</v>
+        <v>27119.88</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>27549.637</v>
       </c>
     </row>
     <row r="6">
@@ -1273,16 +1290,19 @@
         <v>-1169.602</v>
       </c>
       <c r="AK6" t="n">
-        <v>-3366.584</v>
+        <v>-3373.354</v>
       </c>
       <c r="AL6" t="n">
-        <v>6572.886</v>
+        <v>6586.995</v>
       </c>
       <c r="AM6" t="n">
-        <v>915.774</v>
+        <v>924.241</v>
       </c>
       <c r="AN6" t="n">
-        <v>-513.312</v>
+        <v>-532.123</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-791.95</v>
       </c>
     </row>
     <row r="7">
@@ -1405,16 +1425,19 @@
         <v>149917.867</v>
       </c>
       <c r="AK7" t="n">
-        <v>130305.346</v>
+        <v>129448.04</v>
       </c>
       <c r="AL7" t="n">
-        <v>137135.371</v>
+        <v>137251.518</v>
       </c>
       <c r="AM7" t="n">
-        <v>132384.685</v>
+        <v>132639.86</v>
       </c>
       <c r="AN7" t="n">
-        <v>132328.576</v>
+        <v>132464.826</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>129223.641</v>
       </c>
     </row>
     <row r="8">
@@ -1537,16 +1560,19 @@
         <v>169.602</v>
       </c>
       <c r="AK8" t="n">
-        <v>159.069</v>
+        <v>159.641</v>
       </c>
       <c r="AL8" t="n">
-        <v>228.96</v>
+        <v>145.857</v>
       </c>
       <c r="AM8" t="n">
-        <v>120.917</v>
+        <v>121.914</v>
       </c>
       <c r="AN8" t="n">
-        <v>115.484</v>
+        <v>113.187</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>123.109</v>
       </c>
     </row>
     <row r="9">
@@ -1669,16 +1695,19 @@
         <v>149748.265</v>
       </c>
       <c r="AK9" t="n">
-        <v>130146.276</v>
+        <v>129288.399</v>
       </c>
       <c r="AL9" t="n">
-        <v>136906.41</v>
+        <v>137105.662</v>
       </c>
       <c r="AM9" t="n">
-        <v>132263.768</v>
+        <v>132517.946</v>
       </c>
       <c r="AN9" t="n">
-        <v>132213.093</v>
+        <v>132351.639</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>129100.532</v>
       </c>
     </row>
     <row r="10">
@@ -1801,16 +1830,19 @@
         <v>11163.618</v>
       </c>
       <c r="AK10" t="n">
-        <v>3699.829</v>
+        <v>3706.878</v>
       </c>
       <c r="AL10" t="n">
-        <v>4688.825</v>
+        <v>4697.761</v>
       </c>
       <c r="AM10" t="n">
-        <v>7140.531</v>
+        <v>7140.541</v>
       </c>
       <c r="AN10" t="n">
-        <v>10056.497</v>
+        <v>10056.466</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>11223.649</v>
       </c>
     </row>
     <row r="11">
@@ -1933,16 +1965,19 @@
         <v>138584.647</v>
       </c>
       <c r="AK11" t="n">
-        <v>126446.448</v>
+        <v>125581.521</v>
       </c>
       <c r="AL11" t="n">
-        <v>132217.586</v>
+        <v>132407.901</v>
       </c>
       <c r="AM11" t="n">
-        <v>125123.237</v>
+        <v>125377.405</v>
       </c>
       <c r="AN11" t="n">
-        <v>122156.595</v>
+        <v>122295.173</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>117876.882</v>
       </c>
     </row>
     <row r="12">
@@ -2008,6 +2043,7 @@
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2072,6 +2108,7 @@
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2136,6 +2173,7 @@
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2257,16 +2295,19 @@
         <v>118133.161</v>
       </c>
       <c r="AK15" t="n">
-        <v>107604.279</v>
+        <v>106694.544</v>
       </c>
       <c r="AL15" t="n">
-        <v>105696.491</v>
+        <v>105787.198</v>
       </c>
       <c r="AM15" t="n">
-        <v>79538.808</v>
+        <v>79608.28999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>109441.599</v>
+        <v>109565.686</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>106676.646</v>
       </c>
     </row>
     <row r="16">
@@ -2389,16 +2430,19 @@
         <v>2230.509</v>
       </c>
       <c r="AK16" t="n">
-        <v>2498.42</v>
+        <v>2581.64</v>
       </c>
       <c r="AL16" t="n">
-        <v>3520.204</v>
+        <v>3610.13</v>
       </c>
       <c r="AM16" t="n">
-        <v>2246.284</v>
+        <v>2307.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>2541.349</v>
+        <v>2568.642</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2241.211</v>
       </c>
     </row>
     <row r="17">
@@ -2521,16 +2565,19 @@
         <v>8.401999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>24.661</v>
+        <v>24.76</v>
       </c>
       <c r="AL17" t="n">
-        <v>25.79</v>
+        <v>25.909</v>
       </c>
       <c r="AM17" t="n">
-        <v>16.592</v>
+        <v>16.762</v>
       </c>
       <c r="AN17" t="n">
-        <v>13.723</v>
+        <v>13.86</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12.817</v>
       </c>
     </row>
     <row r="18">
@@ -2653,16 +2700,19 @@
         <v>31.511</v>
       </c>
       <c r="AK18" t="n">
-        <v>82.97</v>
+        <v>83.3</v>
       </c>
       <c r="AL18" t="n">
-        <v>61.735</v>
+        <v>62.022</v>
       </c>
       <c r="AM18" t="n">
-        <v>154.786</v>
+        <v>156.548</v>
       </c>
       <c r="AN18" t="n">
-        <v>119.135</v>
+        <v>120.612</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>89.136</v>
       </c>
     </row>
     <row r="19">
@@ -2785,16 +2835,19 @@
         <v>110.959</v>
       </c>
       <c r="AK19" t="n">
-        <v>122.434</v>
+        <v>122.941</v>
       </c>
       <c r="AL19" t="n">
-        <v>371.084</v>
+        <v>372.386</v>
       </c>
       <c r="AM19" t="n">
-        <v>431.108</v>
+        <v>435.573</v>
       </c>
       <c r="AN19" t="n">
-        <v>394.694</v>
+        <v>404.201</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>53.013</v>
       </c>
     </row>
     <row r="20">
@@ -2917,16 +2970,19 @@
         <v>584.203</v>
       </c>
       <c r="AK20" t="n">
-        <v>859.702</v>
+        <v>890.877</v>
       </c>
       <c r="AL20" t="n">
-        <v>1735.782</v>
+        <v>1787.206</v>
       </c>
       <c r="AM20" t="n">
-        <v>41.294</v>
+        <v>41.727</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.2</v>
+        <v>5.264</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1.583</v>
       </c>
     </row>
     <row r="21">
@@ -3049,16 +3105,19 @@
         <v>1495.435</v>
       </c>
       <c r="AK21" t="n">
-        <v>1408.653</v>
+        <v>1459.762</v>
       </c>
       <c r="AL21" t="n">
-        <v>1325.813</v>
+        <v>1362.608</v>
       </c>
       <c r="AM21" t="n">
-        <v>1602.504</v>
+        <v>1657.339</v>
       </c>
       <c r="AN21" t="n">
-        <v>2008.597</v>
+        <v>2024.706</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2084.662</v>
       </c>
     </row>
     <row r="22">
@@ -3190,6 +3249,9 @@
         <v>0</v>
       </c>
       <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3256,6 +3318,7 @@
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3320,6 +3383,7 @@
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -3384,6 +3448,7 @@
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3448,6 +3513,7 @@
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -3512,6 +3578,7 @@
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -3644,6 +3711,9 @@
       <c r="AN28" t="n">
         <v>0</v>
       </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3776,6 +3846,9 @@
       <c r="AN29" t="n">
         <v>0</v>
       </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -3908,6 +3981,9 @@
       <c r="AN30" t="n">
         <v>0</v>
       </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -4029,16 +4105,19 @@
         <v>115902.651</v>
       </c>
       <c r="AK31" t="n">
-        <v>105105.859</v>
+        <v>104112.904</v>
       </c>
       <c r="AL31" t="n">
-        <v>102176.287</v>
+        <v>102177.067</v>
       </c>
       <c r="AM31" t="n">
-        <v>77292.524</v>
+        <v>77300.34</v>
       </c>
       <c r="AN31" t="n">
-        <v>106900.25</v>
+        <v>106997.045</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>104435.434</v>
       </c>
     </row>
     <row r="32">
@@ -4161,16 +4240,19 @@
         <v>113768.373</v>
       </c>
       <c r="AK32" t="n">
-        <v>101534.956</v>
+        <v>100531.334</v>
       </c>
       <c r="AL32" t="n">
-        <v>100569.97</v>
+        <v>100564.928</v>
       </c>
       <c r="AM32" t="n">
-        <v>74116.152</v>
+        <v>74093.92200000001</v>
       </c>
       <c r="AN32" t="n">
-        <v>100829.886</v>
+        <v>100872.131</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>100920.068</v>
       </c>
     </row>
     <row r="33">
@@ -4304,6 +4386,9 @@
       <c r="AN33" t="n">
         <v>0</v>
       </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -4425,16 +4510,19 @@
         <v>2134.278</v>
       </c>
       <c r="AK34" t="n">
-        <v>3570.903</v>
+        <v>3581.571</v>
       </c>
       <c r="AL34" t="n">
-        <v>1606.317</v>
+        <v>1612.139</v>
       </c>
       <c r="AM34" t="n">
-        <v>3176.372</v>
+        <v>3206.418</v>
       </c>
       <c r="AN34" t="n">
-        <v>6070.365</v>
+        <v>6124.914</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>3515.367</v>
       </c>
     </row>
     <row r="35">
@@ -4568,6 +4656,9 @@
       <c r="AN35" t="n">
         <v>0</v>
       </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -4700,6 +4791,9 @@
       <c r="AN36" t="n">
         <v>0</v>
       </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -4832,6 +4926,9 @@
       <c r="AN37" t="n">
         <v>0</v>
       </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -4962,6 +5059,9 @@
         <v>0</v>
       </c>
       <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5028,6 +5128,7 @@
       <c r="AL39" t="inlineStr"/>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -5092,6 +5193,7 @@
       <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -5222,6 +5324,9 @@
         <v>0</v>
       </c>
       <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5288,6 +5393,7 @@
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -5352,6 +5458,7 @@
       <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -5416,6 +5523,7 @@
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -5548,6 +5656,9 @@
       <c r="AN45" t="n">
         <v>0</v>
       </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -5669,16 +5780,19 @@
         <v>113888.599</v>
       </c>
       <c r="AK46" t="n">
-        <v>102532.596</v>
+        <v>103320.889</v>
       </c>
       <c r="AL46" t="n">
-        <v>99764.345</v>
+        <v>100190.222</v>
       </c>
       <c r="AM46" t="n">
-        <v>74915.08900000001</v>
+        <v>75623.23699999999</v>
       </c>
       <c r="AN46" t="n">
-        <v>102413.416</v>
+        <v>102905.342</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>102391.566</v>
       </c>
     </row>
     <row r="47">
@@ -5744,6 +5858,7 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -5808,6 +5923,7 @@
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -5872,6 +5988,7 @@
       <c r="AL49" t="inlineStr"/>
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -5936,6 +6053,7 @@
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -6000,6 +6118,7 @@
       <c r="AL51" t="inlineStr"/>
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -6064,6 +6183,7 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr"/>
       <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -6128,6 +6248,7 @@
       <c r="AL53" t="inlineStr"/>
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -6192,6 +6313,7 @@
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -6256,6 +6378,7 @@
       <c r="AL55" t="inlineStr"/>
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -6320,6 +6443,7 @@
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -6384,6 +6508,7 @@
       <c r="AL57" t="inlineStr"/>
       <c r="AM57" t="inlineStr"/>
       <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -6448,6 +6573,7 @@
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -6512,6 +6638,7 @@
       <c r="AL59" t="inlineStr"/>
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -6576,6 +6703,7 @@
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -6697,16 +6825,19 @@
         <v>113888.599</v>
       </c>
       <c r="AK61" t="n">
-        <v>102532.596</v>
+        <v>103320.889</v>
       </c>
       <c r="AL61" t="n">
-        <v>99764.345</v>
+        <v>100190.222</v>
       </c>
       <c r="AM61" t="n">
-        <v>74915.08900000001</v>
+        <v>75623.23699999999</v>
       </c>
       <c r="AN61" t="n">
-        <v>102413.416</v>
+        <v>102905.342</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>102391.566</v>
       </c>
     </row>
     <row r="62">
@@ -6829,16 +6960,19 @@
         <v>111732.628</v>
       </c>
       <c r="AK62" t="n">
-        <v>98948.70600000001</v>
+        <v>99737.125</v>
       </c>
       <c r="AL62" t="n">
-        <v>98149.10799999999</v>
+        <v>98577.594</v>
       </c>
       <c r="AM62" t="n">
-        <v>71711.56600000001</v>
+        <v>72428.99099999999</v>
       </c>
       <c r="AN62" t="n">
-        <v>96334.735</v>
+        <v>96783.95699999999</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>98867.47500000001</v>
       </c>
     </row>
     <row r="63">
@@ -6972,6 +7106,9 @@
       <c r="AN63" t="n">
         <v>0</v>
       </c>
+      <c r="AO63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -7093,16 +7230,19 @@
         <v>2155.971</v>
       </c>
       <c r="AK64" t="n">
-        <v>3583.89</v>
+        <v>3583.764</v>
       </c>
       <c r="AL64" t="n">
-        <v>1615.237</v>
+        <v>1612.629</v>
       </c>
       <c r="AM64" t="n">
-        <v>3203.523</v>
+        <v>3194.246</v>
       </c>
       <c r="AN64" t="n">
-        <v>6078.681</v>
+        <v>6121.385</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>3524.092</v>
       </c>
     </row>
     <row r="65">
@@ -7236,6 +7376,9 @@
       <c r="AN65" t="n">
         <v>0</v>
       </c>
+      <c r="AO65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -7368,6 +7511,9 @@
       <c r="AN66" t="n">
         <v>0</v>
       </c>
+      <c r="AO66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -7498,6 +7644,9 @@
         <v>0</v>
       </c>
       <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7564,6 +7713,7 @@
       <c r="AL68" t="inlineStr"/>
       <c r="AM68" t="inlineStr"/>
       <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -7628,6 +7778,7 @@
       <c r="AL69" t="inlineStr"/>
       <c r="AM69" t="inlineStr"/>
       <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -7758,6 +7909,9 @@
         <v>0</v>
       </c>
       <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7824,6 +7978,7 @@
       <c r="AL71" t="inlineStr"/>
       <c r="AM71" t="inlineStr"/>
       <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -7888,6 +8043,7 @@
       <c r="AL72" t="inlineStr"/>
       <c r="AM72" t="inlineStr"/>
       <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -7952,6 +8108,7 @@
       <c r="AL73" t="inlineStr"/>
       <c r="AM73" t="inlineStr"/>
       <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -8084,6 +8241,9 @@
       <c r="AN74" t="n">
         <v>0</v>
       </c>
+      <c r="AO74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -8216,6 +8376,9 @@
       <c r="AN75" t="n">
         <v>0</v>
       </c>
+      <c r="AO75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -8337,16 +8500,19 @@
         <v>4014.179</v>
       </c>
       <c r="AK76" t="n">
-        <v>3217.325</v>
+        <v>3682.212</v>
       </c>
       <c r="AL76" t="n">
-        <v>2805.547</v>
+        <v>2944.101</v>
       </c>
       <c r="AM76" t="n">
-        <v>5874.256</v>
+        <v>6245.231</v>
       </c>
       <c r="AN76" t="n">
-        <v>6394.424</v>
+        <v>6357.854</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>6405.656</v>
       </c>
     </row>
     <row r="77">
@@ -8480,6 +8646,9 @@
       <c r="AN77" t="n">
         <v>0</v>
       </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -8612,6 +8781,9 @@
       <c r="AN78" t="n">
         <v>0</v>
       </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -8742,6 +8914,9 @@
         <v>0</v>
       </c>
       <c r="AN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8808,6 +8983,7 @@
       <c r="AL80" t="inlineStr"/>
       <c r="AM80" t="inlineStr"/>
       <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -8938,6 +9114,9 @@
         <v>0</v>
       </c>
       <c r="AN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9004,6 +9183,7 @@
       <c r="AL82" t="inlineStr"/>
       <c r="AM82" t="inlineStr"/>
       <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -9136,6 +9316,9 @@
       <c r="AN83" t="n">
         <v>0</v>
       </c>
+      <c r="AO83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -9268,6 +9451,9 @@
       <c r="AN84" t="n">
         <v>0</v>
       </c>
+      <c r="AO84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -9389,16 +9575,19 @@
         <v>4014.179</v>
       </c>
       <c r="AK85" t="n">
-        <v>3217.325</v>
+        <v>3682.212</v>
       </c>
       <c r="AL85" t="n">
-        <v>2805.547</v>
+        <v>2944.101</v>
       </c>
       <c r="AM85" t="n">
-        <v>5874.256</v>
+        <v>6245.231</v>
       </c>
       <c r="AN85" t="n">
-        <v>6394.424</v>
+        <v>6357.854</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>6405.656</v>
       </c>
     </row>
     <row r="86">
@@ -9464,6 +9653,7 @@
       <c r="AL86" t="inlineStr"/>
       <c r="AM86" t="inlineStr"/>
       <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -9528,6 +9718,7 @@
       <c r="AL87" t="inlineStr"/>
       <c r="AM87" t="inlineStr"/>
       <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -9592,6 +9783,7 @@
       <c r="AL88" t="inlineStr"/>
       <c r="AM88" t="inlineStr"/>
       <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -9656,6 +9848,7 @@
       <c r="AL89" t="inlineStr"/>
       <c r="AM89" t="inlineStr"/>
       <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -9720,6 +9913,7 @@
       <c r="AL90" t="inlineStr"/>
       <c r="AM90" t="inlineStr"/>
       <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -9784,6 +9978,7 @@
       <c r="AL91" t="inlineStr"/>
       <c r="AM91" t="inlineStr"/>
       <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -9916,6 +10111,9 @@
       <c r="AN92" t="n">
         <v>0</v>
       </c>
+      <c r="AO92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -10048,6 +10246,9 @@
       <c r="AN93" t="n">
         <v>0</v>
       </c>
+      <c r="AO93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -10169,16 +10370,19 @@
         <v>130325.905</v>
       </c>
       <c r="AK94" t="n">
-        <v>118157.439</v>
+        <v>118525.654</v>
       </c>
       <c r="AL94" t="n">
-        <v>123479.892</v>
+        <v>123866.825</v>
       </c>
       <c r="AM94" t="n">
-        <v>114625.263</v>
+        <v>115147.121</v>
       </c>
       <c r="AN94" t="n">
-        <v>108733.989</v>
+        <v>109276.974</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>107186.147</v>
       </c>
     </row>
     <row r="95">
@@ -10301,16 +10505,19 @@
         <v>20184.63</v>
       </c>
       <c r="AK95" t="n">
-        <v>19995.421</v>
+        <v>20065.984</v>
       </c>
       <c r="AL95" t="n">
-        <v>20741.69</v>
+        <v>20808.387</v>
       </c>
       <c r="AM95" t="n">
-        <v>16927.68</v>
+        <v>16757.451</v>
       </c>
       <c r="AN95" t="n">
-        <v>15850.401</v>
+        <v>16069.251</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>18222.902</v>
       </c>
     </row>
     <row r="96">
@@ -10433,16 +10640,19 @@
         <v>20013.796</v>
       </c>
       <c r="AK96" t="n">
-        <v>19838.056</v>
+        <v>19908.639</v>
       </c>
       <c r="AL96" t="n">
-        <v>20502.048</v>
+        <v>20568.762</v>
       </c>
       <c r="AM96" t="n">
-        <v>16608.444</v>
+        <v>16518.024</v>
       </c>
       <c r="AN96" t="n">
-        <v>15585.4</v>
+        <v>15870.5</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>18055.607</v>
       </c>
     </row>
     <row r="97">
@@ -10576,6 +10786,9 @@
       <c r="AN97" t="n">
         <v>0</v>
       </c>
+      <c r="AO97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -10697,16 +10910,19 @@
         <v>45.852</v>
       </c>
       <c r="AK98" t="n">
-        <v>42.23</v>
+        <v>42.224</v>
       </c>
       <c r="AL98" t="n">
-        <v>64.32599999999999</v>
+        <v>64.321</v>
       </c>
       <c r="AM98" t="n">
-        <v>85.69</v>
+        <v>64.268</v>
       </c>
       <c r="AN98" t="n">
-        <v>71.13</v>
+        <v>53.347</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>44.909</v>
       </c>
     </row>
     <row r="99">
@@ -10829,16 +11045,19 @@
         <v>19967.944</v>
       </c>
       <c r="AK99" t="n">
-        <v>19795.826</v>
+        <v>19866.414</v>
       </c>
       <c r="AL99" t="n">
-        <v>20437.723</v>
+        <v>20504.442</v>
       </c>
       <c r="AM99" t="n">
-        <v>16522.754</v>
+        <v>16453.756</v>
       </c>
       <c r="AN99" t="n">
-        <v>15514.271</v>
+        <v>15817.153</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>18010.698</v>
       </c>
     </row>
     <row r="100">
@@ -10961,16 +11180,19 @@
         <v>160.733</v>
       </c>
       <c r="AK100" t="n">
-        <v>148.053</v>
+        <v>148.035</v>
       </c>
       <c r="AL100" t="n">
-        <v>225.453</v>
+        <v>225.437</v>
       </c>
       <c r="AM100" t="n">
-        <v>300.333</v>
+        <v>225.25</v>
       </c>
       <c r="AN100" t="n">
-        <v>249.314</v>
+        <v>186.985</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>157.394</v>
       </c>
     </row>
     <row r="101">
@@ -11093,16 +11315,19 @@
         <v>10.102</v>
       </c>
       <c r="AK101" t="n">
-        <v>9.311999999999999</v>
+        <v>9.311</v>
       </c>
       <c r="AL101" t="n">
-        <v>14.189</v>
+        <v>14.188</v>
       </c>
       <c r="AM101" t="n">
-        <v>18.903</v>
+        <v>14.177</v>
       </c>
       <c r="AN101" t="n">
-        <v>15.687</v>
+        <v>11.765</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>9.901</v>
       </c>
     </row>
     <row r="102">
@@ -11225,16 +11450,19 @@
         <v>110136.131</v>
       </c>
       <c r="AK102" t="n">
-        <v>98159.42600000001</v>
+        <v>98457.00900000001</v>
       </c>
       <c r="AL102" t="n">
-        <v>102721.806</v>
+        <v>103038.546</v>
       </c>
       <c r="AM102" t="n">
-        <v>97663.338</v>
+        <v>98341.05100000001</v>
       </c>
       <c r="AN102" t="n">
-        <v>92590.037</v>
+        <v>93209.02899999999</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>88969.655</v>
       </c>
     </row>
     <row r="103">
@@ -11357,16 +11585,19 @@
         <v>3998.806</v>
       </c>
       <c r="AK103" t="n">
-        <v>3431.636</v>
+        <v>3509.063</v>
       </c>
       <c r="AL103" t="n">
-        <v>3707.932</v>
+        <v>3718.687</v>
       </c>
       <c r="AM103" t="n">
-        <v>4553.381</v>
+        <v>4585.923</v>
       </c>
       <c r="AN103" t="n">
-        <v>4709.347</v>
+        <v>4714.084</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>4300.472</v>
       </c>
     </row>
     <row r="104">
@@ -11489,16 +11720,19 @@
         <v>22.282</v>
       </c>
       <c r="AK104" t="n">
-        <v>13.696</v>
+        <v>78.17</v>
       </c>
       <c r="AL104" t="n">
-        <v>95.577</v>
+        <v>95.85299999999999</v>
       </c>
       <c r="AM104" t="n">
-        <v>108.431</v>
+        <v>109.305</v>
       </c>
       <c r="AN104" t="n">
-        <v>112.268</v>
+        <v>112.292</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>114.783</v>
       </c>
     </row>
     <row r="105">
@@ -11621,16 +11855,19 @@
         <v>149.625</v>
       </c>
       <c r="AK105" t="n">
-        <v>197.144</v>
+        <v>200.185</v>
       </c>
       <c r="AL105" t="n">
-        <v>121.833</v>
+        <v>124.605</v>
       </c>
       <c r="AM105" t="n">
-        <v>161.715</v>
+        <v>165.048</v>
       </c>
       <c r="AN105" t="n">
-        <v>147.048</v>
+        <v>144.781</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>68.694</v>
       </c>
     </row>
     <row r="106">
@@ -11753,16 +11990,19 @@
         <v>34.153</v>
       </c>
       <c r="AK106" t="n">
-        <v>35.997</v>
+        <v>36</v>
       </c>
       <c r="AL106" t="n">
-        <v>40.816</v>
+        <v>40.809</v>
       </c>
       <c r="AM106" t="n">
-        <v>38.475</v>
+        <v>38.483</v>
       </c>
       <c r="AN106" t="n">
-        <v>39.349</v>
+        <v>39.319</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>39.276</v>
       </c>
     </row>
     <row r="107">
@@ -11885,16 +12125,19 @@
         <v>601.297</v>
       </c>
       <c r="AK107" t="n">
-        <v>447.256</v>
+        <v>448.25</v>
       </c>
       <c r="AL107" t="n">
-        <v>587.372</v>
+        <v>588.221</v>
       </c>
       <c r="AM107" t="n">
-        <v>602.0839999999999</v>
+        <v>602.909</v>
       </c>
       <c r="AN107" t="n">
-        <v>682.491</v>
+        <v>679.23</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>617.804</v>
       </c>
     </row>
     <row r="108">
@@ -12017,16 +12260,19 @@
         <v>39.547</v>
       </c>
       <c r="AK108" t="n">
-        <v>28.693</v>
+        <v>28.737</v>
       </c>
       <c r="AL108" t="n">
-        <v>31.796</v>
+        <v>31.837</v>
       </c>
       <c r="AM108" t="n">
-        <v>54.288</v>
+        <v>54.454</v>
       </c>
       <c r="AN108" t="n">
-        <v>46.874</v>
+        <v>46.551</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>66.804</v>
       </c>
     </row>
     <row r="109">
@@ -12149,16 +12395,19 @@
         <v>309.646</v>
       </c>
       <c r="AK109" t="n">
-        <v>250.538</v>
+        <v>251.006</v>
       </c>
       <c r="AL109" t="n">
-        <v>287.076</v>
+        <v>287.704</v>
       </c>
       <c r="AM109" t="n">
-        <v>263.528</v>
+        <v>264.62</v>
       </c>
       <c r="AN109" t="n">
-        <v>237.148</v>
+        <v>234.292</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>234.724</v>
       </c>
     </row>
     <row r="110">
@@ -12281,16 +12530,19 @@
         <v>105.712</v>
       </c>
       <c r="AK110" t="n">
-        <v>92.976</v>
+        <v>93.22799999999999</v>
       </c>
       <c r="AL110" t="n">
-        <v>76.73099999999999</v>
+        <v>76.093</v>
       </c>
       <c r="AM110" t="n">
-        <v>82.789</v>
+        <v>83.348</v>
       </c>
       <c r="AN110" t="n">
-        <v>76.26300000000001</v>
+        <v>76.488</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>76.31999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -12413,16 +12665,19 @@
         <v>131.591</v>
       </c>
       <c r="AK111" t="n">
-        <v>112.632</v>
+        <v>112.876</v>
       </c>
       <c r="AL111" t="n">
-        <v>133.929</v>
+        <v>134.348</v>
       </c>
       <c r="AM111" t="n">
-        <v>330.522</v>
+        <v>332.793</v>
       </c>
       <c r="AN111" t="n">
-        <v>455.024</v>
+        <v>454.401</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>208.286</v>
       </c>
     </row>
     <row r="112">
@@ -12545,16 +12800,19 @@
         <v>58.276</v>
       </c>
       <c r="AK112" t="n">
-        <v>37.748</v>
+        <v>37.88</v>
       </c>
       <c r="AL112" t="n">
-        <v>44.863</v>
+        <v>45.055</v>
       </c>
       <c r="AM112" t="n">
-        <v>81.292</v>
+        <v>81.962</v>
       </c>
       <c r="AN112" t="n">
-        <v>102.843</v>
+        <v>100.564</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>51.321</v>
       </c>
     </row>
     <row r="113">
@@ -12677,16 +12935,19 @@
         <v>85.35299999999999</v>
       </c>
       <c r="AK113" t="n">
-        <v>64.913</v>
+        <v>65.12</v>
       </c>
       <c r="AL113" t="n">
-        <v>51.698</v>
+        <v>51.842</v>
       </c>
       <c r="AM113" t="n">
-        <v>52.604</v>
+        <v>52.986</v>
       </c>
       <c r="AN113" t="n">
-        <v>41.783</v>
+        <v>41.746</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>45.785</v>
       </c>
     </row>
     <row r="114">
@@ -12809,16 +13070,19 @@
         <v>2414.241</v>
       </c>
       <c r="AK114" t="n">
-        <v>2118.436</v>
+        <v>2125.888</v>
       </c>
       <c r="AL114" t="n">
-        <v>2173.811</v>
+        <v>2179.6</v>
       </c>
       <c r="AM114" t="n">
-        <v>2733.726</v>
+        <v>2755.749</v>
       </c>
       <c r="AN114" t="n">
-        <v>2724.281</v>
+        <v>2740.972</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>2753.235</v>
       </c>
     </row>
     <row r="115">
@@ -12941,16 +13205,19 @@
         <v>5.426</v>
       </c>
       <c r="AK115" t="n">
-        <v>3.622</v>
+        <v>3.636</v>
       </c>
       <c r="AL115" t="n">
-        <v>4.545</v>
+        <v>4.578</v>
       </c>
       <c r="AM115" t="n">
-        <v>3.007</v>
+        <v>3.037</v>
       </c>
       <c r="AN115" t="n">
-        <v>5.59</v>
+        <v>5.36</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>3.872</v>
       </c>
     </row>
     <row r="116">
@@ -13073,16 +13340,19 @@
         <v>41.658</v>
       </c>
       <c r="AK116" t="n">
-        <v>27.983</v>
+        <v>28.086</v>
       </c>
       <c r="AL116" t="n">
-        <v>57.887</v>
+        <v>58.143</v>
       </c>
       <c r="AM116" t="n">
-        <v>40.919</v>
+        <v>41.228</v>
       </c>
       <c r="AN116" t="n">
-        <v>38.385</v>
+        <v>38.088</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>19.568</v>
       </c>
     </row>
     <row r="117">
@@ -13205,16 +13475,19 @@
         <v>90862.91099999999</v>
       </c>
       <c r="AK117" t="n">
-        <v>79271.673</v>
+        <v>79391.084</v>
       </c>
       <c r="AL117" t="n">
-        <v>82426.628</v>
+        <v>82687.645</v>
       </c>
       <c r="AM117" t="n">
-        <v>78657.61</v>
+        <v>79168.986</v>
       </c>
       <c r="AN117" t="n">
-        <v>76201.745</v>
+        <v>76715.00599999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>74275.954</v>
       </c>
     </row>
     <row r="118">
@@ -13337,16 +13610,19 @@
         <v>367.126</v>
       </c>
       <c r="AK118" t="n">
-        <v>322.701</v>
+        <v>323.861</v>
       </c>
       <c r="AL118" t="n">
-        <v>322.017</v>
+        <v>322.869</v>
       </c>
       <c r="AM118" t="n">
-        <v>319.736</v>
+        <v>322.373</v>
       </c>
       <c r="AN118" t="n">
-        <v>293.838</v>
+        <v>296.417</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>272.23</v>
       </c>
     </row>
     <row r="119">
@@ -13469,16 +13745,19 @@
         <v>89863.605</v>
       </c>
       <c r="AK119" t="n">
-        <v>78663.005</v>
+        <v>78779.916</v>
       </c>
       <c r="AL119" t="n">
-        <v>81773.60799999999</v>
+        <v>82032.317</v>
       </c>
       <c r="AM119" t="n">
-        <v>77853.651</v>
+        <v>78359.66099999999</v>
       </c>
       <c r="AN119" t="n">
-        <v>75412.25</v>
+        <v>75923.295</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>73506.966</v>
       </c>
     </row>
     <row r="120">
@@ -13601,16 +13880,19 @@
         <v>300.159</v>
       </c>
       <c r="AK120" t="n">
-        <v>194.049</v>
+        <v>195.14</v>
       </c>
       <c r="AL120" t="n">
-        <v>191.027</v>
+        <v>192.192</v>
       </c>
       <c r="AM120" t="n">
-        <v>210.955</v>
+        <v>211.677</v>
       </c>
       <c r="AN120" t="n">
-        <v>214.981</v>
+        <v>215.71</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>204.431</v>
       </c>
     </row>
     <row r="121">
@@ -13733,16 +14015,19 @@
         <v>332.022</v>
       </c>
       <c r="AK121" t="n">
-        <v>91.91800000000001</v>
+        <v>92.167</v>
       </c>
       <c r="AL121" t="n">
-        <v>139.976</v>
+        <v>140.266</v>
       </c>
       <c r="AM121" t="n">
-        <v>273.267</v>
+        <v>275.275</v>
       </c>
       <c r="AN121" t="n">
-        <v>280.677</v>
+        <v>279.584</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>292.327</v>
       </c>
     </row>
     <row r="122">
@@ -13876,6 +14161,9 @@
       <c r="AN122" t="n">
         <v>0</v>
       </c>
+      <c r="AO122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -14008,6 +14296,9 @@
       <c r="AN123" t="n">
         <v>0</v>
       </c>
+      <c r="AO123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -14129,16 +14420,19 @@
         <v>15274.414</v>
       </c>
       <c r="AK124" t="n">
-        <v>15456.117</v>
+        <v>15556.862</v>
       </c>
       <c r="AL124" t="n">
-        <v>16587.247</v>
+        <v>16632.215</v>
       </c>
       <c r="AM124" t="n">
-        <v>14452.348</v>
+        <v>14586.142</v>
       </c>
       <c r="AN124" t="n">
-        <v>11678.944</v>
+        <v>11779.939</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>10393.229</v>
       </c>
     </row>
     <row r="125">
@@ -14261,16 +14555,19 @@
         <v>2052.49</v>
       </c>
       <c r="AK125" t="n">
-        <v>1987.568</v>
+        <v>1994.397</v>
       </c>
       <c r="AL125" t="n">
-        <v>2484.713</v>
+        <v>2493.989</v>
       </c>
       <c r="AM125" t="n">
-        <v>2131.742</v>
+        <v>2148.512</v>
       </c>
       <c r="AN125" t="n">
-        <v>1257.642</v>
+        <v>1270.494</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1254.915</v>
       </c>
     </row>
     <row r="126">
@@ -14393,16 +14690,19 @@
         <v>10695.826</v>
       </c>
       <c r="AK126" t="n">
-        <v>10961.368</v>
+        <v>10999.5</v>
       </c>
       <c r="AL126" t="n">
-        <v>11492.671</v>
+        <v>11519.491</v>
       </c>
       <c r="AM126" t="n">
-        <v>9723.512000000001</v>
+        <v>9818.816000000001</v>
       </c>
       <c r="AN126" t="n">
-        <v>7887.309</v>
+        <v>7956.011</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>6580.424</v>
       </c>
     </row>
     <row r="127">
@@ -14525,16 +14825,19 @@
         <v>2526.098</v>
       </c>
       <c r="AK127" t="n">
-        <v>2507.182</v>
+        <v>2556.95</v>
       </c>
       <c r="AL127" t="n">
-        <v>2602.382</v>
+        <v>2611.097</v>
       </c>
       <c r="AM127" t="n">
-        <v>2589.434</v>
+        <v>2610.918</v>
       </c>
       <c r="AN127" t="n">
-        <v>2526.243</v>
+        <v>2545.465</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2549.912</v>
       </c>
     </row>
     <row r="128">
@@ -14657,16 +14960,19 @@
         <v>0</v>
       </c>
       <c r="AK128" t="n">
-        <v>0</v>
+        <v>6.015</v>
       </c>
       <c r="AL128" t="n">
-        <v>7.48</v>
+        <v>7.639</v>
       </c>
       <c r="AM128" t="n">
-        <v>7.66</v>
+        <v>7.896</v>
       </c>
       <c r="AN128" t="n">
-        <v>7.751</v>
+        <v>7.968</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>7.978</v>
       </c>
     </row>
     <row r="129">
@@ -14800,6 +15106,9 @@
       <c r="AN129" t="n">
         <v>0</v>
       </c>
+      <c r="AO129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -14921,16 +15230,19 @@
         <v>5.144</v>
       </c>
       <c r="AK130" t="n">
-        <v>2.591</v>
+        <v>2.661</v>
       </c>
       <c r="AL130" t="n">
-        <v>16.396</v>
+        <v>19.892</v>
       </c>
       <c r="AM130" t="n">
-        <v>34.244</v>
+        <v>48.62</v>
       </c>
       <c r="AN130" t="n">
-        <v>293.551</v>
+        <v>-1.305</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>-6.411</v>
       </c>
     </row>
     <row r="131">
@@ -15053,16 +15365,19 @@
         <v>692.593</v>
       </c>
       <c r="AK131" t="n">
-        <v>725.965</v>
+        <v>725.9640000000001</v>
       </c>
       <c r="AL131" t="n">
-        <v>709.373</v>
+        <v>709.372</v>
       </c>
       <c r="AM131" t="n">
         <v>665.53</v>
       </c>
       <c r="AN131" t="n">
-        <v>781.3049999999999</v>
+        <v>781.306</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>718.878</v>
       </c>
     </row>
     <row r="132">
@@ -15188,13 +15503,16 @@
         <v>6.606</v>
       </c>
       <c r="AL132" t="n">
-        <v>3.528</v>
+        <v>3.527</v>
       </c>
       <c r="AM132" t="n">
-        <v>2.412</v>
+        <v>2.411</v>
       </c>
       <c r="AN132" t="n">
         <v>1.904</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="133">
@@ -15326,7 +15644,10 @@
         <v>23.036</v>
       </c>
       <c r="AN133" t="n">
-        <v>17.246</v>
+        <v>17.247</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>10.924</v>
       </c>
     </row>
     <row r="134">
@@ -15460,6 +15781,9 @@
       <c r="AN134" t="n">
         <v>2.242</v>
       </c>
+      <c r="AO134" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -15581,16 +15905,19 @@
         <v>427.863</v>
       </c>
       <c r="AK135" t="n">
-        <v>363.234</v>
+        <v>363.233</v>
       </c>
       <c r="AL135" t="n">
         <v>212.969</v>
       </c>
       <c r="AM135" t="n">
-        <v>623.684</v>
+        <v>623.6849999999999</v>
       </c>
       <c r="AN135" t="n">
         <v>759.913</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>705.974</v>
       </c>
     </row>
     <row r="136">
@@ -15716,13 +16043,16 @@
         <v>703.704</v>
       </c>
       <c r="AL136" t="n">
-        <v>980.138</v>
+        <v>976.295</v>
       </c>
       <c r="AM136" t="n">
-        <v>998.938</v>
+        <v>996.659</v>
       </c>
       <c r="AN136" t="n">
-        <v>1119.164</v>
+        <v>1121.159</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>756.239</v>
       </c>
     </row>
     <row r="137">
@@ -15856,6 +16186,9 @@
       <c r="AN137" t="n">
         <v>84.462</v>
       </c>
+      <c r="AO137" t="n">
+        <v>61.096</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -15980,13 +16313,16 @@
         <v>108.666</v>
       </c>
       <c r="AL138" t="n">
-        <v>342.278</v>
+        <v>338.436</v>
       </c>
       <c r="AM138" t="n">
-        <v>399.386</v>
+        <v>397.107</v>
       </c>
       <c r="AN138" t="n">
-        <v>357.849</v>
+        <v>359.845</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>45.685</v>
       </c>
     </row>
     <row r="139">
@@ -16120,6 +16456,9 @@
       <c r="AN139" t="n">
         <v>676.852</v>
       </c>
+      <c r="AO139" t="n">
+        <v>649.458</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -16250,6 +16589,9 @@
         <v>0</v>
       </c>
       <c r="AN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO140" t="n">
         <v>0</v>
       </c>
     </row>
